--- a/stories/arbres/ATOM-TMP.SAI.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila marche au parc avec papa. Papa dit : il y a quatre saisons. Au printemps, Lila voit des fleurs. En été, il fait chaud. Lila boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Lila met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Lila répète : quatre saisons.</t>
+          <t>Lila marche au parc avec papa. Il y a quatre saisons. Au printemps, Lila voit des fleurs. En été, il fait chaud. Lila boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Lila met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Lila répète : quatre saisons.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila marche au parc avec papa.
+papa|Il y a quatre saisons. Au printemps, Lila voit des fleurs. En été, il fait chaud.
+narrateur|Lila boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Lila met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Lila répète : quatre saisons.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Il fait chaud. Quelle saison est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a nommé les quatre saisons. Un signe chacune. Papa l'a aidée.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lila ramasse une feuille. Papa tient sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SAI.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Lila boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Lila met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Lila répète : quatre saisons.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Il fait chaud. Quelle saison est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Lila a nommé les quatre saisons. Un signe chacune. Papa l'a aidée.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Lila ramasse une feuille. Papa tient sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SAI.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les saisons de Lila</t>
+          <t>Le tas rouge de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut un tas de feuilles rouges. Le vent l'éparpille. Papa et elle recommencent. Le tas revient près du banc.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila marche au parc avec papa. Il y a quatre saisons. Au printemps, Lila voit des fleurs. En été, il fait chaud. Lila boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Lila met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Lila répète : quatre saisons.</t>
+          <t>Une feuille rouge colle au banc du parc. Le bois du banc est froid. Ça sent la terre mouillée. Une mousse verte tient au bois. Un oiseau pique une graine. Le bec tape, tout petit. Papa boutonne le manteau. Le vent passe dans les arbres. Des feuilles tombent, tout doux. Tu as vu la feuille rouge ? Elle est rouge. Oui. En ce moment, Sarah la ramasse. Elle est sèche, un peu cassante. Ses doigts sont froids, un peu rouges. Je veux un tas. Un tas de feuilles ? Un grand tas. On en ramasse beaucoup. Sarah prend une feuille jaune. Elle la pose près du banc. Papa en apporte une brune. Le tas est encore petit. Encore. Ils marchent sous l'arbre. Les feuilles craquent, sous les bottes. Ça fait cric, cric. Sarah pousse avec le pied. Le tas monte un peu. Il devient grand. Encore des rouges. Une feuille rouge vole. Sarah court un peu. Elle l'attrape. Elle la pose sur le tas. Une feuille jaune tient dans les cheveux. Elle s'est accrochée. Je la prends. En été, elles sont vertes. Là, elles sont rouges. Oui. C'est l'automne. Le tas arrive aux genoux. Il est beau. Le ciel est bas, tout gris. Un vent fort arrive. Il vient de la rue. Les feuilles s'envolent. Le tas s'éparpille. Oh. Mon tas. Le vent l'a pris. On recommence ? Oui. Sarah court après une feuille. Papa en ramasse trois. Ils les portent au banc. Le tas recommence, tout bas. Tu veux encore des rouges ? Oui, des rouges.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila marche au parc avec papa. Papa dit : il y a &lt;emphasis level="moderate"&gt;quatre&lt;/emphasis&gt; saisons. Au printemps, Lila voit des fleurs. En été, il fait chaud. Lila boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Lila met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Lila répète : quatre saisons.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille rouge colle au banc du parc. Le bois du banc est froid. Ça sent la terre mouillée. Une mousse verte tient au bois. Un oiseau pique une graine. Le bec tape, tout petit. Papa boutonne le manteau. Le vent passe dans les arbres. Des feuilles tombent, tout doux. Tu as vu la feuille rouge ? Elle est rouge. Oui. En ce moment, Sarah la ramasse. Elle est sèche, un peu cassante. Ses doigts sont froids, un peu rouges. Je veux un tas. Un tas de feuilles ? Un grand tas. On en ramasse beaucoup. Sarah prend une feuille jaune. Elle la pose près du banc. Papa en apporte une brune. Le tas est encore petit. Encore. Ils marchent sous l'arbre. Les feuilles craquent, sous les bottes. Ça fait cric, cric. Sarah pousse avec le pied. Le tas monte un peu. Il devient grand. Encore des rouges. Une feuille rouge vole. Sarah court un peu. Elle l'attrape. Elle la pose sur le tas. Une feuille jaune tient dans les cheveux. Elle s'est accrochée. Je la prends. En été, elles sont vertes. Là, elles sont rouges. Oui. C'est l'automne. Le tas arrive aux genoux. Il est beau. Le ciel est bas, tout gris. Un vent fort arrive. Il vient de la rue. Les feuilles s'envolent. Le tas s'éparpille. Oh. Mon tas. Le vent l'a pris. On recommence ? Oui. Sarah court après une feuille. Papa en ramasse trois. Ils les portent au banc. Le tas recommence, tout bas. Tu veux encore des rouges ? Oui, des rouges.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,9 +1324,66 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Lila marche au parc avec papa.
-papa|Il y a quatre saisons. Au printemps, Lila voit des fleurs. En été, il fait chaud.
-narrateur|Lila boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Lila met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Lila répète : quatre saisons.</t>
+          <t>narrateur|Une feuille rouge colle au banc du parc.
+narrateur|Le bois du banc est froid.
+narrateur|Ça sent la terre mouillée.
+narrateur|Une mousse verte tient au bois.
+narrateur|Un oiseau pique une graine.
+narrateur|Le bec tape, tout petit.
+narrateur|Papa boutonne le manteau.
+narrateur|Le vent passe dans les arbres.
+narrateur|Des feuilles tombent, tout doux.
+papa|Tu as vu la feuille rouge ?
+enfant-f|Elle est rouge.
+papa|Oui.
+narrateur|En ce moment, Sarah la ramasse.
+narrateur|Elle est sèche, un peu cassante.
+narrateur|Ses doigts sont froids, un peu rouges.
+enfant-f|Je veux un tas.
+papa|Un tas de feuilles ?
+enfant-f|Un grand tas.
+papa|On en ramasse beaucoup.
+narrateur|Sarah prend une feuille jaune.
+narrateur|Elle la pose près du banc.
+narrateur|Papa en apporte une brune.
+narrateur|Le tas est encore petit.
+enfant-f|Encore.
+narrateur|Ils marchent sous l'arbre.
+narrateur|Les feuilles craquent, sous les bottes.
+narrateur|Ça fait cric, cric.
+narrateur|Sarah pousse avec le pied.
+narrateur|Le tas monte un peu.
+papa|Il devient grand.
+enfant-f|Encore des rouges.
+narrateur|Une feuille rouge vole.
+narrateur|Sarah court un peu.
+narrateur|Elle l'attrape.
+narrateur|Elle la pose sur le tas.
+narrateur|Une feuille jaune tient dans les cheveux.
+papa|Elle s'est accrochée.
+enfant-f|Je la prends.
+papa|En été, elles sont vertes.
+enfant-f|Là, elles sont rouges.
+papa|Oui.
+papa|C'est l'automne.
+narrateur|Le tas arrive aux genoux.
+enfant-f|Il est beau.
+narrateur|Le ciel est bas, tout gris.
+narrateur|Un vent fort arrive.
+narrateur|Il vient de la rue.
+narrateur|Les feuilles s'envolent.
+narrateur|Le tas s'éparpille.
+enfant-f|Oh.
+enfant-f|Mon tas.
+papa|Le vent l'a pris.
+papa|On recommence ?
+enfant-f|Oui.
+narrateur|Sarah court après une feuille.
+narrateur|Papa en ramasse trois.
+narrateur|Ils les portent au banc.
+narrateur|Le tas recommence, tout bas.
+papa|Tu veux encore des rouges ?
+enfant-f|Oui, des rouges.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,12 +1415,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Il fait chaud. Quelle saison est-ce ?</t>
+          <t>Les feuilles sont rouges. Quelle saison est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Il fait chaud. Quelle saison est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les feuilles sont rouges. Quelle saison est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1361,12 +1430,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>été</t>
+          <t>automne</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>été | l'été | en été</t>
+          <t>automne | l'automne | en automne | feuilles | rouge</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1450,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>En été, il fait chaud. Quelle saison ?</t>
+          <t>Les feuilles sont rouges. Quelle saison ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1499,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1571,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Il fait chaud. Quelle saison est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Les feuilles sont rouges.
+narrateur|Quelle saison est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila a nommé les quatre saisons. Un signe chacune. Papa l'a aidée.</t>
+          <t>Sarah pousse encore, tout doux. Papa tient le tas avec le bras. Le vent passe, plus faible. Il reste. Oui. On le garde près du banc. Une feuille rouge tombe sur le chapeau. Papa la pose tout en haut. Le tas est revenu. Bravo, Sarah. Tu as recommencé. Des petits bouts collent aux bottes. Sarah souffle sur une feuille. Elle ne vole plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila a nommé les &lt;emphasis level="moderate"&gt;quatre&lt;/emphasis&gt; saisons. Un signe chacune. Papa l'a aidée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pousse encore, tout doux. Papa tient le tas avec le bras. Le vent passe, plus faible. Il reste. Oui. On le garde près du banc. Une feuille rouge tombe sur le chapeau. Papa la pose tout en haut. Le tas est revenu. Bravo, Sarah. Tu as recommencé. Des petits bouts collent aux bottes. Sarah souffle sur une feuille. Elle ne vole plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1591,14 +1660,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,10 +1743,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lila a nommé les quatre saisons. Un signe chacune. Papa l'a aidée.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah pousse encore, tout doux.
+narrateur|Papa tient le tas avec le bras.
+narrateur|Le vent passe, plus faible.
+enfant-f|Il reste.
+papa|Oui.
+papa|On le garde près du banc.
+narrateur|Une feuille rouge tombe sur le chapeau.
+narrateur|Papa la pose tout en haut.
+enfant-f|Le tas est revenu.
+papa|Bravo, Sarah.
+papa|Tu as recommencé.
+narrateur|Des petits bouts collent aux bottes.
+narrateur|Sarah souffle sur une feuille.
+narrateur|Elle ne vole plus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Lila ramasse une feuille. Papa tient sa main.</t>
+          <t>Ils s'assoient sur le banc froid. Le tas est là, tout près. Il est à nous. Oui. Sarah tient une feuille rouge. Elle la fait tourner. L'automne sent la terre. Et les feuilles.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila ramasse &lt;emphasis level="moderate"&gt;un&lt;/emphasis&gt;e feuille. Papa tient sa main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils s'assoient sur le banc froid. Le tas est là, tout près. Il est à nous. Oui. Sarah tient une feuille rouge. Elle la fait tourner. L'automne sent la terre. Et les feuilles.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1763,14 +1844,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1842,10 +1923,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Lila ramasse une feuille. Papa tient sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils s'assoient sur le banc froid.
+narrateur|Le tas est là, tout près.
+enfant-f|Il est à nous.
+papa|Oui.
+narrateur|Sarah tient une feuille rouge.
+narrateur|Elle la fait tourner.
+papa|L'automne sent la terre.
+enfant-f|Et les feuilles.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le soleil est bas, tout jaune. Le tas fait une ombre ronde. Je le garde. On le regardera encore. Sarah pose la feuille sur ses genoux. Le parc craque, tout doucement.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soleil est bas, tout jaune. Le tas fait une ombre ronde. Je le garde. On le regardera encore. Sarah pose la feuille sur ses genoux. Le parc craque, tout doucement.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1931,14 +2018,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2010,10 +2097,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le soleil est bas, tout jaune.
+narrateur|Le tas fait une ombre ronde.
+enfant-f|Je le garde.
+papa|On le regardera encore.
+narrateur|Sarah pose la feuille sur ses genoux.
+narrateur|Le parc craque, tout doucement.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SAI.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc en automne, banc, feuilles</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lila, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
